--- a/mlef_pipeline/results/DCR/SQUAMOUS/training_summary.xlsx
+++ b/mlef_pipeline/results/DCR/SQUAMOUS/training_summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W3"/>
+  <dimension ref="A1:W12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,138 +548,138 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RWD_DP</t>
+          <t>RWD</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7586206896551724</v>
+        <v>0.6792864943574809</v>
       </c>
       <c r="C2" t="n">
-        <v>0.08234876241514089</v>
+        <v>0.05488777741816009</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6282381050328931</v>
+        <v>0.5769334810654833</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05243815262827625</v>
+        <v>0.05587501313549149</v>
       </c>
       <c r="F2" t="n">
-        <v>0.664953399122807</v>
+        <v>0.7170255629288486</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1518887579381689</v>
+        <v>0.1393107724919586</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6157446946169772</v>
+        <v>0.479305602686146</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2105315688156912</v>
+        <v>0.04513816967838</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7254901960784315</v>
+        <v>0.6787252368647717</v>
       </c>
       <c r="K2" t="n">
-        <v>0.241169655716295</v>
+        <v>0.1322096780373492</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5801217038539555</v>
+        <v>0.5043896913055792</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.9534883720930233</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.1481481481481481</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5625</v>
+        <v>0.7692307692307694</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3402326346970275</v>
+        <v>0.1805589456165395</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5607843137254902</v>
+        <v>0.325</v>
       </c>
       <c r="R2" t="n">
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>11</v>
       </c>
       <c r="U2" t="n">
-        <v>128</v>
+        <v>365</v>
       </c>
       <c r="V2" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="W2" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RWD_DP/rwd-only</t>
+          <t>RWD_DP</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5871921182266011</v>
+        <v>0.752216748768473</v>
       </c>
       <c r="C3" t="n">
-        <v>0.09929445346480414</v>
+        <v>0.08326372214825184</v>
       </c>
       <c r="D3" t="n">
-        <v>0.464665990843431</v>
+        <v>0.6189179780875645</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1109445889417622</v>
+        <v>0.04986333727616173</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6805555555555556</v>
+        <v>0.6653874269005848</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2835128448219099</v>
+        <v>0.1699489432466569</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4079038884575569</v>
+        <v>0.6042863612836439</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2561506736377154</v>
+        <v>0.2585434792258175</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6666666666666665</v>
+        <v>0.5980392156862746</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2884860884013651</v>
+        <v>0.2638699759306735</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3947368421052632</v>
+        <v>0.5548387096774194</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8823529411764706</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O3" t="n">
-        <v>0.859375</v>
+        <v>0.578125</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1810334093698053</v>
+        <v>0.3334710547813069</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5151515151515151</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="R3" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="T3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U3" t="n">
         <v>128</v>
@@ -689,6 +689,661 @@
       </c>
       <c r="W3" t="n">
         <v>16</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RWD_DP/rwd-only</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.6354679802955667</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.09641798921022038</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5581027349386725</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.05863166399109527</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.6912434895833334</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.2871728021132689</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.5648380887681159</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.2758655442538087</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.6470588235294117</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.2764271108462212</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.5818181818181818</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.828125</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.2013972565393641</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.6761133603238867</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T4" t="n">
+        <v>11</v>
+      </c>
+      <c r="U4" t="n">
+        <v>128</v>
+      </c>
+      <c r="V4" t="n">
+        <v>23</v>
+      </c>
+      <c r="W4" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>RWD_FMRAD</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.8441051136363635</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.06309745929588328</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.719406049437198</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.1155130592443651</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.7899608744787068</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.1087360941760753</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.6818450190160718</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.2280374445349756</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.706959706959707</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.1873293599312315</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.7153488372093023</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.9444444444444445</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.1047724346860932</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.8705882352941177</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="T5" t="n">
+        <v>11</v>
+      </c>
+      <c r="U5" t="n">
+        <v>152</v>
+      </c>
+      <c r="V5" t="n">
+        <v>34</v>
+      </c>
+      <c r="W5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RWD_FMRAD/rwd-only</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.6477272727272727</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.08859203206718858</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.4847790947595872</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.1340862554575372</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.7733781410763751</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.2083640415173216</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.3372553981106612</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.2780661228445576</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.750915750915751</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.1914973298464099</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.6421052631578947</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.6190476190476191</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.326660664090009</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>7</v>
+      </c>
+      <c r="U6" t="n">
+        <v>152</v>
+      </c>
+      <c r="V6" t="n">
+        <v>34</v>
+      </c>
+      <c r="W6" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RWD_PYRAD</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.6717568146139574</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.08210228247625417</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.5477777175245518</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.1173730246780647</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.6049812030075189</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.2272215272406568</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.5856863240791812</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.2829374923109848</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5110294117647058</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.2076373241321321</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.3265306122448979</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.1142857142857143</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.1993017984199738</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.3684210526315789</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>11</v>
+      </c>
+      <c r="U7" t="n">
+        <v>168</v>
+      </c>
+      <c r="V7" t="n">
+        <v>33</v>
+      </c>
+      <c r="W7" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>RWD_PYRAD/rwd-only</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.5922648779791637</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.08637688842983904</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.3289617111934067</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.05577654669411335</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3765306122448979</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.4572631796219896</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.6274092970521542</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.4589431838184173</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.6176470588235294</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.2040671691624985</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.5170731707317073</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2941176470588235</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.1714285714285714</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.2555991633881653</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.3684210526315789</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>11</v>
+      </c>
+      <c r="U8" t="n">
+        <v>168</v>
+      </c>
+      <c r="V8" t="n">
+        <v>33</v>
+      </c>
+      <c r="W8" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>RWD_DP_FMRAD</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.4722222222222223</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.3274159498707438</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.4615384615384616</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.4596522980886497</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>14</v>
+      </c>
+      <c r="U9" t="n">
+        <v>47</v>
+      </c>
+      <c r="V9" t="n">
+        <v>13</v>
+      </c>
+      <c r="W9" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>RWD_DP_FMRAD/rwd-only</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.5851449275362319</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.1729323029950036</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.2385680513340088</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.05118518349116152</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.425531914893617</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.4944234058988192</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.574468085106383</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.4944234058988192</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.3055555555555556</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.2990262073004202</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.2200227919088827</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U10" t="n">
+        <v>47</v>
+      </c>
+      <c r="V10" t="n">
+        <v>13</v>
+      </c>
+      <c r="W10" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>RWD_DP_PYRAD</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.7533333333333334</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.1386682402183254</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.6833195592286501</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.1626692259494416</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.7149783549783549</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.2542362877881476</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.7233333333333333</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.2725969385541425</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.3916523775672831</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.4484848484848485</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.4800000000000001</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.4503654357659453</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.5238095238095238</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>6</v>
+      </c>
+      <c r="U11" t="n">
+        <v>55</v>
+      </c>
+      <c r="V11" t="n">
+        <v>13</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>RWD_DP_PYRAD/rwd-only</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.4973333333333334</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.157135008059585</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.2413723776223776</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.06581578438307643</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.4979295977319692</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.509090909090909</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.4999173485406371</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.5972222222222223</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.3224749730607461</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.5751633986928104</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.4400000000000001</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.4120588305990788</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.4505494505494506</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T12" t="n">
+        <v>6</v>
+      </c>
+      <c r="U12" t="n">
+        <v>55</v>
+      </c>
+      <c r="V12" t="n">
+        <v>13</v>
+      </c>
+      <c r="W12" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/mlef_pipeline/results/DCR/SQUAMOUS/training_summary.xlsx
+++ b/mlef_pipeline/results/DCR/SQUAMOUS/training_summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W3"/>
+  <dimension ref="A1:W12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,147 +548,804 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RWD_FMRAD</t>
+          <t>RWD</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7906593406593407</v>
+        <v>0.6772843101565343</v>
       </c>
       <c r="C2" t="n">
-        <v>0.06857619041526641</v>
+        <v>0.05438162135483882</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7400581052386149</v>
+        <v>0.4107491404827618</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05710696245757012</v>
+        <v>0.0592682324054218</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7952427176803907</v>
+        <v>0.7035779272054893</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1243735040036065</v>
+        <v>0.3609963674086463</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7377324693114167</v>
+        <v>0.3936765234095162</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1633865998408509</v>
+        <v>0.359156846413769</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5104166666666667</v>
+        <v>0.5865633074935402</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2050054059824725</v>
+        <v>0.1429148140433532</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4889478337754199</v>
+        <v>0.4857142857142857</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.9069767441860465</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6875</v>
+        <v>0.1481481481481481</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4571428571428572</v>
+        <v>0.6181318681318682</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3578388287434314</v>
+        <v>0.2192895183114685</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5804195804195804</v>
+        <v>0.5</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="T2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="U2" t="n">
-        <v>171</v>
+        <v>365</v>
       </c>
       <c r="V2" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="W2" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>RWD_DP</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.7699507389162563</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.08023266408426744</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.6553047345556537</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.0479016334586978</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.6484774762426901</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.1789085231674049</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.7002685041407868</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.1712369286183751</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.6176470588235294</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.2660473734397198</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.486815415821501</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.5294117647058824</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.546875</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.346089048143073</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.6190476190476191</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>12</v>
+      </c>
+      <c r="U3" t="n">
+        <v>128</v>
+      </c>
+      <c r="V3" t="n">
+        <v>23</v>
+      </c>
+      <c r="W3" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RWD_DP/rwd-only</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.6630541871921183</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.09489115121961444</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.548091960682376</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.06073128781496723</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.6678059895833334</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.3141591005232149</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.5783045419254659</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.2410062179915158</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.5588235294117649</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.2891891684232575</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.4888888888888889</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.703125</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.2886783998798486</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T4" t="n">
+        <v>11</v>
+      </c>
+      <c r="U4" t="n">
+        <v>128</v>
+      </c>
+      <c r="V4" t="n">
+        <v>23</v>
+      </c>
+      <c r="W4" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>RWD_FMRAD</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.7906593406593407</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.06857619041526641</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.7400581052386149</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.05710696245757012</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.7952427176803907</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.1243735040036065</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.7377324693114167</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.1633865998408509</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.5104166666666667</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.2050054059824726</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.4889478337754199</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.4571428571428572</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.3578388287434314</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.5804195804195804</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="T5" t="n">
+        <v>12</v>
+      </c>
+      <c r="U5" t="n">
+        <v>171</v>
+      </c>
+      <c r="V5" t="n">
+        <v>34</v>
+      </c>
+      <c r="W5" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>RWD_FMRAD/rwd-only</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>0.5794642857142858</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.0866035751902163</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.3313516584391012</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.07361156593289102</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.405886511149669</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.4449101645497543</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.5736563631300474</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.4461363210265398</v>
-      </c>
-      <c r="J3" t="n">
+      <c r="B6" t="n">
+        <v>0.5506868131868132</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.08725394774245318</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.3404726075086186</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.046580274850938</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.3950497025289269</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.4338243450628947</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.5696516064937117</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.402305049344542</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.3368055555555556</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.1913861337153026</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.3061224489795918</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.2285714285714286</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.3101082591321981</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.3684210526315789</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>11</v>
+      </c>
+      <c r="U6" t="n">
+        <v>171</v>
+      </c>
+      <c r="V6" t="n">
+        <v>34</v>
+      </c>
+      <c r="W6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RWD_PYRAD</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.6716141001855287</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.08228408570200585</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.5633423932702661</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.09390250597322512</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.6061448263515933</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.2129126523223322</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.6043478427406999</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.2586974224638096</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.2089853830810134</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.3265306122448979</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.1142857142857143</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.1993017984199738</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.3684210526315789</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>11</v>
+      </c>
+      <c r="U7" t="n">
+        <v>168</v>
+      </c>
+      <c r="V7" t="n">
+        <v>33</v>
+      </c>
+      <c r="W7" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>RWD_PYRAD/rwd-only</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.6086770372484658</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.08555822809923919</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.3392799252703876</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.0586572474017481</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3887486573576799</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.4472817079884877</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.6158021541950113</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.4495941188970226</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.6397058823529411</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.1984385126005274</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.6278195488721805</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.4705882352941176</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.2285714285714286</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.3101082591321981</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.2941176470588235</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="T8" t="n">
+        <v>11</v>
+      </c>
+      <c r="U8" t="n">
+        <v>168</v>
+      </c>
+      <c r="V8" t="n">
+        <v>33</v>
+      </c>
+      <c r="W8" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>RWD_DP_FMRAD</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.9428571428571428</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.05565122528837374</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.5113473092998956</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.2966087784866139</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.7881226053639847</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.2879505987750145</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.5689655172413793</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.4952209178050025</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.3611111111111112</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.3960425333425137</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.4052287581699346</v>
+      </c>
+      <c r="M9" t="n">
         <v>0.5555555555555556</v>
       </c>
-      <c r="K3" t="n">
-        <v>0.2002544138240882</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.4623255813953489</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.2222222222222222</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.5428571428571429</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.3782522198099554</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.2941176470588235</v>
-      </c>
-      <c r="R3" t="n">
+      <c r="N9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.3958933188174818</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.4505494505494506</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>9</v>
+      </c>
+      <c r="U9" t="n">
+        <v>58</v>
+      </c>
+      <c r="V9" t="n">
+        <v>13</v>
+      </c>
+      <c r="W9" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>RWD_DP_FMRAD/rwd-only</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.4869047619047619</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.1528411761815432</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.2913647056966023</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.1483912836549738</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4936781609195402</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.4458603503061938</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.5344827586206896</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.4988095221203253</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.3611111111111112</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.3450471831715481</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.4090909090909091</v>
+      </c>
+      <c r="M10" t="n">
         <v>1</v>
       </c>
-      <c r="S3" t="n">
+      <c r="N10" t="n">
         <v>0</v>
       </c>
-      <c r="T3" t="n">
+      <c r="O10" t="n">
+        <v>0.9600000000000001</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.07543615297398709</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.898989898989899</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T10" t="n">
         <v>11</v>
       </c>
-      <c r="U3" t="n">
-        <v>171</v>
-      </c>
-      <c r="V3" t="n">
-        <v>34</v>
-      </c>
-      <c r="W3" t="n">
+      <c r="U10" t="n">
+        <v>58</v>
+      </c>
+      <c r="V10" t="n">
+        <v>13</v>
+      </c>
+      <c r="W10" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>RWD_DP_PYRAD</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.1417616785312755</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.6567004074357016</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.1193250712692944</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.7143722943722944</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.1550084374296087</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.6244444444444445</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1751497675631946</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.3830435817405414</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.5599999999999999</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.4258131706943348</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.4505494505494506</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T11" t="n">
         <v>12</v>
+      </c>
+      <c r="U11" t="n">
+        <v>55</v>
+      </c>
+      <c r="V11" t="n">
+        <v>13</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>RWD_DP_PYRAD/rwd-only</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.5393333333333333</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.1548639741497626</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.2534935897435898</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.04872110582029027</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.4979295977319692</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.4979295977319692</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.3905255083508211</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.5125</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.2985328200384402</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.2929292929292929</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>6</v>
+      </c>
+      <c r="U12" t="n">
+        <v>55</v>
+      </c>
+      <c r="V12" t="n">
+        <v>13</v>
+      </c>
+      <c r="W12" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
